--- a/Check.xlsx
+++ b/Check.xlsx
@@ -154,8 +154,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CheckData" displayName="CheckData" ref="A1:J65" headerRowCount="1">
-  <autoFilter ref="A1:J65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CheckData" displayName="CheckData" ref="A1:J89" headerRowCount="1">
+  <autoFilter ref="A1:J89"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Раздел"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3493,6 +3493,1254 @@
       <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Зависимость тестовой среды / данных, дефект приложения не установлен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="96" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CHK-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Успешная авторизация в тёмной теме</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="96" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CHK-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / доступность</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Читаемость введённого логина в тёмной теме</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-002 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-002-dark-auth.png; Bugs.xlsx: BUG-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="96" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CHK-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Новостей на Главную через меню</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CHK-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Панели управления на Главную</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="96" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CHK-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Панели управления в Новости</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="96" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CHK-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Переход из Нашей миссии в Новости</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="96" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CHK-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Системный Back из Нашей миссии возвращает на Главную</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="96" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CHK-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Системный Back из Панели управления возвращает в Новости</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="96" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CHK-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Навигация</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Переход ALL NEWS с главного экрана</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="96" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CHK-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Выход из раздела Новостей</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="96" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CHK-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Выход из Панели управления</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="96" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>CHK-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Авторизация / навигация</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Выход из Нашей миссии</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="96" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CHK-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Создание</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённая отмена создания заполненной новости</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="96" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CHK-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Удаление</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Отмена удаления сохраняет собственную новость</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="96" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CHK-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Удаление</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённое удаление сохраняется после повторного открытия панели</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="96" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>CHK-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение изменённого заголовка собственной новости</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="96" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>CHK-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение категории, описания, даты и времени новости</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="96" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>CHK-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённая отмена редактирования сохраняет исходные данные</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="96" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>CHK-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Отмена диалога отмены сохраняет черновик редактирования</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="96" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>CHK-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / дата</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение календаря без изменений сохраняет дату публикации</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-003 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-003-date-picker.png; Bugs.xlsx: BUG-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="96" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>CHK-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / время</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждение выбора времени без изменений сохраняет 23:47</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-003 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-003-time-picker.png; Bugs.xlsx: BUG-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="96" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>CHK-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование / активность</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение переключения активности собственной новости</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="96" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>CHK-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Новости / фильтрация</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Сброс пустого фильтра восстанавливает ленту без сообщения о пустом списке</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест подтвердил ожидаемый результат.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>allure-results.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="96" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>CHK-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Навигация / доступность новости</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Созданная опубликованная новость доступна после перехода между разделами</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Не пройден (UI)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>UI-автотест не пройден. См. BUG-004 в Bugs.xlsx.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>26.10.2026</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Android 16 / API 36; x86_64; Pixel 6, 1080×2400; en-US; GMT / UTC; debug 1.0.0 (14); AGP 8.12.2 / Gradle 8.13. UI-автотест.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>docs/evidence/expanded-2026-10-26/BUG-004-news-after-navigation.png; Bugs.xlsx: BUG-004</t>
         </is>
       </c>
     </row>
